--- a/Transportation/road_traffic_offences.xlsx
+++ b/Transportation/road_traffic_offences.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="25">
   <si>
     <t>year</t>
   </si>
@@ -65,6 +65,9 @@
   </si>
   <si>
     <t>BAN (EXPRESS)</t>
+  </si>
+  <si>
+    <t>CARS</t>
   </si>
   <si>
     <t>BUS/PICK UP SHUTTLE</t>
@@ -443,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D365"/>
+  <dimension ref="A1:D417"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -471,7 +474,7 @@
         <v>17</v>
       </c>
       <c r="D2">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -485,7 +488,7 @@
         <v>18</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -499,7 +502,7 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -513,7 +516,7 @@
         <v>20</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -527,7 +530,7 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -541,7 +544,7 @@
         <v>22</v>
       </c>
       <c r="D7">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -555,7 +558,7 @@
         <v>23</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -563,13 +566,13 @@
         <v>2019</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D9">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -580,10 +583,10 @@
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D10">
-        <v>4</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -594,10 +597,10 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -608,10 +611,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -622,7 +625,7 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -636,10 +639,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D14">
-        <v>50</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -650,10 +653,10 @@
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D15">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -661,13 +664,13 @@
         <v>2019</v>
       </c>
       <c r="B16" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D16">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -675,13 +678,13 @@
         <v>2019</v>
       </c>
       <c r="B17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C17" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D17">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -692,10 +695,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -706,10 +709,10 @@
         <v>6</v>
       </c>
       <c r="C19" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D19">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -720,10 +723,10 @@
         <v>6</v>
       </c>
       <c r="C20" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -734,7 +737,7 @@
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -748,10 +751,10 @@
         <v>6</v>
       </c>
       <c r="C22" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -759,13 +762,13 @@
         <v>2019</v>
       </c>
       <c r="B23" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C23" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D23">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -773,10 +776,10 @@
         <v>2019</v>
       </c>
       <c r="B24" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -787,10 +790,10 @@
         <v>2019</v>
       </c>
       <c r="B25" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C25" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -804,7 +807,7 @@
         <v>7</v>
       </c>
       <c r="C26" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -818,10 +821,10 @@
         <v>7</v>
       </c>
       <c r="C27" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -832,7 +835,7 @@
         <v>7</v>
       </c>
       <c r="C28" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -846,7 +849,7 @@
         <v>7</v>
       </c>
       <c r="C29" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -857,10 +860,10 @@
         <v>2019</v>
       </c>
       <c r="B30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C30" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -871,10 +874,10 @@
         <v>2019</v>
       </c>
       <c r="B31" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C31" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -885,10 +888,10 @@
         <v>2019</v>
       </c>
       <c r="B32" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C32" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -899,10 +902,10 @@
         <v>2019</v>
       </c>
       <c r="B33" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C33" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -916,7 +919,7 @@
         <v>8</v>
       </c>
       <c r="C34" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -930,7 +933,7 @@
         <v>8</v>
       </c>
       <c r="C35" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -944,7 +947,7 @@
         <v>8</v>
       </c>
       <c r="C36" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -955,10 +958,10 @@
         <v>2019</v>
       </c>
       <c r="B37" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C37" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -969,10 +972,10 @@
         <v>2019</v>
       </c>
       <c r="B38" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C38" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -983,10 +986,10 @@
         <v>2019</v>
       </c>
       <c r="B39" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C39" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -997,10 +1000,10 @@
         <v>2019</v>
       </c>
       <c r="B40" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C40" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -1011,10 +1014,10 @@
         <v>2019</v>
       </c>
       <c r="B41" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C41" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -1028,7 +1031,7 @@
         <v>9</v>
       </c>
       <c r="C42" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -1042,7 +1045,7 @@
         <v>9</v>
       </c>
       <c r="C43" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -1053,10 +1056,10 @@
         <v>2019</v>
       </c>
       <c r="B44" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C44" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -1067,10 +1070,10 @@
         <v>2019</v>
       </c>
       <c r="B45" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C45" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -1081,10 +1084,10 @@
         <v>2019</v>
       </c>
       <c r="B46" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C46" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -1095,10 +1098,10 @@
         <v>2019</v>
       </c>
       <c r="B47" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C47" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -1109,10 +1112,10 @@
         <v>2019</v>
       </c>
       <c r="B48" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C48" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -1123,10 +1126,10 @@
         <v>2019</v>
       </c>
       <c r="B49" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C49" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -1140,7 +1143,7 @@
         <v>10</v>
       </c>
       <c r="C50" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -1151,13 +1154,13 @@
         <v>2019</v>
       </c>
       <c r="B51" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C51" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D51">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1165,13 +1168,13 @@
         <v>2019</v>
       </c>
       <c r="B52" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C52" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D52">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1179,10 +1182,10 @@
         <v>2019</v>
       </c>
       <c r="B53" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C53" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -1193,10 +1196,10 @@
         <v>2019</v>
       </c>
       <c r="B54" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C54" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -1207,10 +1210,10 @@
         <v>2019</v>
       </c>
       <c r="B55" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C55" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -1221,10 +1224,10 @@
         <v>2019</v>
       </c>
       <c r="B56" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C56" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -1235,13 +1238,13 @@
         <v>2019</v>
       </c>
       <c r="B57" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C57" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D57">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1249,7 +1252,7 @@
         <v>2019</v>
       </c>
       <c r="B58" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C58" t="s">
         <v>17</v>
@@ -1263,13 +1266,13 @@
         <v>2019</v>
       </c>
       <c r="B59" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C59" t="s">
         <v>18</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1277,13 +1280,13 @@
         <v>2019</v>
       </c>
       <c r="B60" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C60" t="s">
         <v>19</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1291,7 +1294,7 @@
         <v>2019</v>
       </c>
       <c r="B61" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C61" t="s">
         <v>20</v>
@@ -1305,7 +1308,7 @@
         <v>2019</v>
       </c>
       <c r="B62" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C62" t="s">
         <v>21</v>
@@ -1319,7 +1322,7 @@
         <v>2019</v>
       </c>
       <c r="B63" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C63" t="s">
         <v>22</v>
@@ -1333,7 +1336,7 @@
         <v>2019</v>
       </c>
       <c r="B64" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C64" t="s">
         <v>23</v>
@@ -1347,13 +1350,13 @@
         <v>2019</v>
       </c>
       <c r="B65" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C65" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D65">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1361,13 +1364,13 @@
         <v>2019</v>
       </c>
       <c r="B66" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C66" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D66">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1375,13 +1378,13 @@
         <v>2019</v>
       </c>
       <c r="B67" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C67" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1389,10 +1392,10 @@
         <v>2019</v>
       </c>
       <c r="B68" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C68" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -1403,10 +1406,10 @@
         <v>2019</v>
       </c>
       <c r="B69" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C69" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -1417,13 +1420,13 @@
         <v>2019</v>
       </c>
       <c r="B70" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C70" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D70">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1431,10 +1434,10 @@
         <v>2019</v>
       </c>
       <c r="B71" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C71" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -1445,10 +1448,10 @@
         <v>2019</v>
       </c>
       <c r="B72" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C72" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -1459,10 +1462,10 @@
         <v>2019</v>
       </c>
       <c r="B73" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C73" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -1473,10 +1476,10 @@
         <v>2019</v>
       </c>
       <c r="B74" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C74" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -1487,13 +1490,13 @@
         <v>2019</v>
       </c>
       <c r="B75" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C75" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1501,13 +1504,13 @@
         <v>2019</v>
       </c>
       <c r="B76" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C76" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -1515,10 +1518,10 @@
         <v>2019</v>
       </c>
       <c r="B77" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C77" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -1529,10 +1532,10 @@
         <v>2019</v>
       </c>
       <c r="B78" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C78" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -1543,10 +1546,10 @@
         <v>2019</v>
       </c>
       <c r="B79" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C79" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -1557,13 +1560,13 @@
         <v>2019</v>
       </c>
       <c r="B80" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C80" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -1571,10 +1574,10 @@
         <v>2019</v>
       </c>
       <c r="B81" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C81" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -1585,10 +1588,10 @@
         <v>2019</v>
       </c>
       <c r="B82" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C82" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -1599,10 +1602,10 @@
         <v>2019</v>
       </c>
       <c r="B83" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C83" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -1613,10 +1616,10 @@
         <v>2019</v>
       </c>
       <c r="B84" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C84" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -1627,10 +1630,10 @@
         <v>2019</v>
       </c>
       <c r="B85" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C85" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -1641,10 +1644,10 @@
         <v>2019</v>
       </c>
       <c r="B86" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C86" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -1655,10 +1658,10 @@
         <v>2019</v>
       </c>
       <c r="B87" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C87" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -1669,10 +1672,10 @@
         <v>2019</v>
       </c>
       <c r="B88" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C88" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -1683,10 +1686,10 @@
         <v>2019</v>
       </c>
       <c r="B89" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C89" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -1697,10 +1700,10 @@
         <v>2019</v>
       </c>
       <c r="B90" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C90" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -1711,13 +1714,13 @@
         <v>2019</v>
       </c>
       <c r="B91" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C91" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D91">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -1725,52 +1728,52 @@
         <v>2019</v>
       </c>
       <c r="B92" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C92" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D92">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B93" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C93" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D93">
-        <v>110</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B94" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C94" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D94">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B95" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C95" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -1778,41 +1781,41 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B96" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C96" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D96">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B97" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C97" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D97">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B98" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C98" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -1820,13 +1823,13 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B99" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C99" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -1834,41 +1837,41 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B100" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C100" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D100">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B101" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C101" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D101">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B102" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C102" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -1876,44 +1879,44 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B103" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C103" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D103">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B104" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C104" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D104">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B105" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C105" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D105">
-        <v>109</v>
+        <v>64</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -1921,13 +1924,13 @@
         <v>2020</v>
       </c>
       <c r="B106" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C106" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D106">
-        <v>150</v>
+        <v>120</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -1935,13 +1938,13 @@
         <v>2020</v>
       </c>
       <c r="B107" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C107" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D107">
-        <v>10</v>
+        <v>110</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -1949,13 +1952,13 @@
         <v>2020</v>
       </c>
       <c r="B108" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C108" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D108">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -1963,10 +1966,10 @@
         <v>2020</v>
       </c>
       <c r="B109" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C109" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -1977,13 +1980,13 @@
         <v>2020</v>
       </c>
       <c r="B110" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C110" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D110">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -1991,13 +1994,13 @@
         <v>2020</v>
       </c>
       <c r="B111" t="s">
+        <v>4</v>
+      </c>
+      <c r="C111" t="s">
+        <v>22</v>
+      </c>
+      <c r="D111">
         <v>6</v>
-      </c>
-      <c r="C111" t="s">
-        <v>21</v>
-      </c>
-      <c r="D111">
-        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2005,10 +2008,10 @@
         <v>2020</v>
       </c>
       <c r="B112" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C112" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -2019,10 +2022,10 @@
         <v>2020</v>
       </c>
       <c r="B113" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C113" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -2033,13 +2036,13 @@
         <v>2020</v>
       </c>
       <c r="B114" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C114" t="s">
         <v>17</v>
       </c>
       <c r="D114">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2047,13 +2050,13 @@
         <v>2020</v>
       </c>
       <c r="B115" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C115" t="s">
         <v>18</v>
       </c>
       <c r="D115">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2061,13 +2064,13 @@
         <v>2020</v>
       </c>
       <c r="B116" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C116" t="s">
         <v>19</v>
       </c>
       <c r="D116">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2075,7 +2078,7 @@
         <v>2020</v>
       </c>
       <c r="B117" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C117" t="s">
         <v>20</v>
@@ -2089,13 +2092,13 @@
         <v>2020</v>
       </c>
       <c r="B118" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C118" t="s">
         <v>21</v>
       </c>
       <c r="D118">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2103,13 +2106,13 @@
         <v>2020</v>
       </c>
       <c r="B119" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C119" t="s">
         <v>22</v>
       </c>
       <c r="D119">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2117,13 +2120,13 @@
         <v>2020</v>
       </c>
       <c r="B120" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C120" t="s">
         <v>23</v>
       </c>
       <c r="D120">
-        <v>0</v>
+        <v>109</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2131,13 +2134,13 @@
         <v>2020</v>
       </c>
       <c r="B121" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C121" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D121">
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2145,13 +2148,13 @@
         <v>2020</v>
       </c>
       <c r="B122" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C122" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D122">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2159,13 +2162,13 @@
         <v>2020</v>
       </c>
       <c r="B123" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C123" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D123">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2173,10 +2176,10 @@
         <v>2020</v>
       </c>
       <c r="B124" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C124" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D124">
         <v>0</v>
@@ -2187,10 +2190,10 @@
         <v>2020</v>
       </c>
       <c r="B125" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C125" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -2201,10 +2204,10 @@
         <v>2020</v>
       </c>
       <c r="B126" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C126" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D126">
         <v>0</v>
@@ -2215,10 +2218,10 @@
         <v>2020</v>
       </c>
       <c r="B127" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C127" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -2229,10 +2232,10 @@
         <v>2020</v>
       </c>
       <c r="B128" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C128" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D128">
         <v>0</v>
@@ -2243,10 +2246,10 @@
         <v>2020</v>
       </c>
       <c r="B129" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C129" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D129">
         <v>0</v>
@@ -2257,10 +2260,10 @@
         <v>2020</v>
       </c>
       <c r="B130" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C130" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D130">
         <v>0</v>
@@ -2271,10 +2274,10 @@
         <v>2020</v>
       </c>
       <c r="B131" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C131" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D131">
         <v>0</v>
@@ -2285,10 +2288,10 @@
         <v>2020</v>
       </c>
       <c r="B132" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C132" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D132">
         <v>0</v>
@@ -2299,10 +2302,10 @@
         <v>2020</v>
       </c>
       <c r="B133" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C133" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D133">
         <v>0</v>
@@ -2313,10 +2316,10 @@
         <v>2020</v>
       </c>
       <c r="B134" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C134" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D134">
         <v>0</v>
@@ -2327,10 +2330,10 @@
         <v>2020</v>
       </c>
       <c r="B135" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C135" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D135">
         <v>0</v>
@@ -2341,10 +2344,10 @@
         <v>2020</v>
       </c>
       <c r="B136" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C136" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D136">
         <v>0</v>
@@ -2355,10 +2358,10 @@
         <v>2020</v>
       </c>
       <c r="B137" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C137" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D137">
         <v>0</v>
@@ -2369,10 +2372,10 @@
         <v>2020</v>
       </c>
       <c r="B138" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C138" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D138">
         <v>0</v>
@@ -2383,10 +2386,10 @@
         <v>2020</v>
       </c>
       <c r="B139" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C139" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D139">
         <v>0</v>
@@ -2397,13 +2400,13 @@
         <v>2020</v>
       </c>
       <c r="B140" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C140" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D140">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -2411,10 +2414,10 @@
         <v>2020</v>
       </c>
       <c r="B141" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C141" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D141">
         <v>0</v>
@@ -2425,13 +2428,13 @@
         <v>2020</v>
       </c>
       <c r="B142" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C142" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D142">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -2439,13 +2442,13 @@
         <v>2020</v>
       </c>
       <c r="B143" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C143" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D143">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -2453,10 +2456,10 @@
         <v>2020</v>
       </c>
       <c r="B144" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C144" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D144">
         <v>0</v>
@@ -2467,10 +2470,10 @@
         <v>2020</v>
       </c>
       <c r="B145" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C145" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D145">
         <v>0</v>
@@ -2481,10 +2484,10 @@
         <v>2020</v>
       </c>
       <c r="B146" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C146" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D146">
         <v>0</v>
@@ -2495,10 +2498,10 @@
         <v>2020</v>
       </c>
       <c r="B147" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C147" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D147">
         <v>0</v>
@@ -2509,10 +2512,10 @@
         <v>2020</v>
       </c>
       <c r="B148" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C148" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D148">
         <v>0</v>
@@ -2523,10 +2526,10 @@
         <v>2020</v>
       </c>
       <c r="B149" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C149" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D149">
         <v>0</v>
@@ -2537,10 +2540,10 @@
         <v>2020</v>
       </c>
       <c r="B150" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C150" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D150">
         <v>0</v>
@@ -2551,10 +2554,10 @@
         <v>2020</v>
       </c>
       <c r="B151" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C151" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D151">
         <v>0</v>
@@ -2565,10 +2568,10 @@
         <v>2020</v>
       </c>
       <c r="B152" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C152" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D152">
         <v>0</v>
@@ -2579,10 +2582,10 @@
         <v>2020</v>
       </c>
       <c r="B153" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C153" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D153">
         <v>0</v>
@@ -2593,10 +2596,10 @@
         <v>2020</v>
       </c>
       <c r="B154" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C154" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D154">
         <v>0</v>
@@ -2607,10 +2610,10 @@
         <v>2020</v>
       </c>
       <c r="B155" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C155" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D155">
         <v>0</v>
@@ -2621,10 +2624,10 @@
         <v>2020</v>
       </c>
       <c r="B156" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C156" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D156">
         <v>0</v>
@@ -2635,10 +2638,10 @@
         <v>2020</v>
       </c>
       <c r="B157" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C157" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D157">
         <v>0</v>
@@ -2649,10 +2652,10 @@
         <v>2020</v>
       </c>
       <c r="B158" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C158" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D158">
         <v>0</v>
@@ -2663,10 +2666,10 @@
         <v>2020</v>
       </c>
       <c r="B159" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C159" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D159">
         <v>0</v>
@@ -2677,10 +2680,10 @@
         <v>2020</v>
       </c>
       <c r="B160" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C160" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D160">
         <v>0</v>
@@ -2691,10 +2694,10 @@
         <v>2020</v>
       </c>
       <c r="B161" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C161" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D161">
         <v>0</v>
@@ -2705,13 +2708,13 @@
         <v>2020</v>
       </c>
       <c r="B162" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C162" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D162">
-        <v>60</v>
+        <v>20</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -2719,13 +2722,13 @@
         <v>2020</v>
       </c>
       <c r="B163" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C163" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D163">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -2733,13 +2736,13 @@
         <v>2020</v>
       </c>
       <c r="B164" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C164" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D164">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -2747,10 +2750,10 @@
         <v>2020</v>
       </c>
       <c r="B165" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C165" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D165">
         <v>0</v>
@@ -2761,10 +2764,10 @@
         <v>2020</v>
       </c>
       <c r="B166" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C166" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D166">
         <v>0</v>
@@ -2775,10 +2778,10 @@
         <v>2020</v>
       </c>
       <c r="B167" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C167" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D167">
         <v>0</v>
@@ -2789,10 +2792,10 @@
         <v>2020</v>
       </c>
       <c r="B168" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C168" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D168">
         <v>0</v>
@@ -2803,10 +2806,10 @@
         <v>2020</v>
       </c>
       <c r="B169" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C169" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D169">
         <v>0</v>
@@ -2817,7 +2820,7 @@
         <v>2020</v>
       </c>
       <c r="B170" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C170" t="s">
         <v>17</v>
@@ -2831,7 +2834,7 @@
         <v>2020</v>
       </c>
       <c r="B171" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C171" t="s">
         <v>18</v>
@@ -2845,7 +2848,7 @@
         <v>2020</v>
       </c>
       <c r="B172" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C172" t="s">
         <v>19</v>
@@ -2859,7 +2862,7 @@
         <v>2020</v>
       </c>
       <c r="B173" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C173" t="s">
         <v>20</v>
@@ -2873,7 +2876,7 @@
         <v>2020</v>
       </c>
       <c r="B174" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C174" t="s">
         <v>21</v>
@@ -2887,7 +2890,7 @@
         <v>2020</v>
       </c>
       <c r="B175" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C175" t="s">
         <v>22</v>
@@ -2901,7 +2904,7 @@
         <v>2020</v>
       </c>
       <c r="B176" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C176" t="s">
         <v>23</v>
@@ -2915,10 +2918,10 @@
         <v>2020</v>
       </c>
       <c r="B177" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C177" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D177">
         <v>0</v>
@@ -2929,10 +2932,10 @@
         <v>2020</v>
       </c>
       <c r="B178" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C178" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D178">
         <v>0</v>
@@ -2943,10 +2946,10 @@
         <v>2020</v>
       </c>
       <c r="B179" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C179" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D179">
         <v>0</v>
@@ -2957,10 +2960,10 @@
         <v>2020</v>
       </c>
       <c r="B180" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C180" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D180">
         <v>0</v>
@@ -2971,10 +2974,10 @@
         <v>2020</v>
       </c>
       <c r="B181" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C181" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D181">
         <v>0</v>
@@ -2985,13 +2988,13 @@
         <v>2020</v>
       </c>
       <c r="B182" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C182" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D182">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -2999,52 +3002,52 @@
         <v>2020</v>
       </c>
       <c r="B183" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C183" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D183">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:4">
       <c r="A184">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B184" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C184" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D184">
-        <v>110</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:4">
       <c r="A185">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B185" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C185" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D185">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="186" spans="1:4">
       <c r="A186">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B186" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C186" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D186">
         <v>0</v>
@@ -3052,55 +3055,55 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B187" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C187" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D187">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:4">
       <c r="A188">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B188" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C188" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D188">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189" spans="1:4">
       <c r="A189">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B189" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C189" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D189">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:4">
       <c r="A190">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B190" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C190" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D190">
         <v>0</v>
@@ -3108,41 +3111,41 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B191" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C191" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D191">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:4">
       <c r="A192">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B192" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C192" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D192">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193" spans="1:4">
       <c r="A193">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B193" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C193" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D193">
         <v>0</v>
@@ -3150,13 +3153,13 @@
     </row>
     <row r="194" spans="1:4">
       <c r="A194">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B194" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C194" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D194">
         <v>0</v>
@@ -3164,69 +3167,69 @@
     </row>
     <row r="195" spans="1:4">
       <c r="A195">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B195" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C195" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D195">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:4">
       <c r="A196">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B196" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C196" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D196">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:4">
       <c r="A197">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B197" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C197" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D197">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:4">
       <c r="A198">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B198" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C198" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D198">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:4">
       <c r="A199">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B199" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C199" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D199">
         <v>0</v>
@@ -3234,13 +3237,13 @@
     </row>
     <row r="200" spans="1:4">
       <c r="A200">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B200" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C200" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D200">
         <v>0</v>
@@ -3248,41 +3251,41 @@
     </row>
     <row r="201" spans="1:4">
       <c r="A201">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B201" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C201" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D201">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202" spans="1:4">
       <c r="A202">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B202" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C202" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D202">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203" spans="1:4">
       <c r="A203">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B203" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C203" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D203">
         <v>0</v>
@@ -3290,13 +3293,13 @@
     </row>
     <row r="204" spans="1:4">
       <c r="A204">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B204" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C204" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D204">
         <v>0</v>
@@ -3304,27 +3307,27 @@
     </row>
     <row r="205" spans="1:4">
       <c r="A205">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B205" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C205" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D205">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206" spans="1:4">
       <c r="A206">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B206" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C206" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D206">
         <v>0</v>
@@ -3332,13 +3335,13 @@
     </row>
     <row r="207" spans="1:4">
       <c r="A207">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B207" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C207" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D207">
         <v>0</v>
@@ -3346,30 +3349,30 @@
     </row>
     <row r="208" spans="1:4">
       <c r="A208">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B208" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C208" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D208">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="209" spans="1:4">
       <c r="A209">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B209" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C209" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D209">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -3377,13 +3380,13 @@
         <v>2021</v>
       </c>
       <c r="B210" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C210" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D210">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -3391,13 +3394,13 @@
         <v>2021</v>
       </c>
       <c r="B211" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C211" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D211">
-        <v>0</v>
+        <v>110</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -3405,13 +3408,13 @@
         <v>2021</v>
       </c>
       <c r="B212" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C212" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D212">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -3419,13 +3422,13 @@
         <v>2021</v>
       </c>
       <c r="B213" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C213" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D213">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -3433,13 +3436,13 @@
         <v>2021</v>
       </c>
       <c r="B214" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C214" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D214">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -3447,13 +3450,13 @@
         <v>2021</v>
       </c>
       <c r="B215" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C215" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D215">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -3461,13 +3464,13 @@
         <v>2021</v>
       </c>
       <c r="B216" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C216" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D216">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -3475,10 +3478,10 @@
         <v>2021</v>
       </c>
       <c r="B217" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C217" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D217">
         <v>0</v>
@@ -3489,13 +3492,13 @@
         <v>2021</v>
       </c>
       <c r="B218" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C218" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D218">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -3503,13 +3506,13 @@
         <v>2021</v>
       </c>
       <c r="B219" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C219" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D219">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -3517,13 +3520,13 @@
         <v>2021</v>
       </c>
       <c r="B220" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C220" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D220">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -3531,10 +3534,10 @@
         <v>2021</v>
       </c>
       <c r="B221" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C221" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D221">
         <v>0</v>
@@ -3545,10 +3548,10 @@
         <v>2021</v>
       </c>
       <c r="B222" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C222" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D222">
         <v>0</v>
@@ -3559,13 +3562,13 @@
         <v>2021</v>
       </c>
       <c r="B223" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C223" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D223">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -3573,13 +3576,13 @@
         <v>2021</v>
       </c>
       <c r="B224" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C224" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D224">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -3587,13 +3590,13 @@
         <v>2021</v>
       </c>
       <c r="B225" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C225" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D225">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -3601,13 +3604,13 @@
         <v>2021</v>
       </c>
       <c r="B226" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C226" t="s">
         <v>17</v>
       </c>
       <c r="D226">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -3615,13 +3618,13 @@
         <v>2021</v>
       </c>
       <c r="B227" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C227" t="s">
         <v>18</v>
       </c>
       <c r="D227">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -3629,7 +3632,7 @@
         <v>2021</v>
       </c>
       <c r="B228" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C228" t="s">
         <v>19</v>
@@ -3643,7 +3646,7 @@
         <v>2021</v>
       </c>
       <c r="B229" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C229" t="s">
         <v>20</v>
@@ -3657,13 +3660,13 @@
         <v>2021</v>
       </c>
       <c r="B230" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C230" t="s">
         <v>21</v>
       </c>
       <c r="D230">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -3671,13 +3674,13 @@
         <v>2021</v>
       </c>
       <c r="B231" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C231" t="s">
         <v>22</v>
       </c>
       <c r="D231">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -3685,7 +3688,7 @@
         <v>2021</v>
       </c>
       <c r="B232" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C232" t="s">
         <v>23</v>
@@ -3699,13 +3702,13 @@
         <v>2021</v>
       </c>
       <c r="B233" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C233" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D233">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -3713,13 +3716,13 @@
         <v>2021</v>
       </c>
       <c r="B234" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C234" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D234">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -3727,13 +3730,13 @@
         <v>2021</v>
       </c>
       <c r="B235" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C235" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D235">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -3741,10 +3744,10 @@
         <v>2021</v>
       </c>
       <c r="B236" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C236" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D236">
         <v>0</v>
@@ -3755,10 +3758,10 @@
         <v>2021</v>
       </c>
       <c r="B237" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C237" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D237">
         <v>0</v>
@@ -3769,10 +3772,10 @@
         <v>2021</v>
       </c>
       <c r="B238" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C238" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D238">
         <v>0</v>
@@ -3783,13 +3786,13 @@
         <v>2021</v>
       </c>
       <c r="B239" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C239" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D239">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -3797,13 +3800,13 @@
         <v>2021</v>
       </c>
       <c r="B240" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C240" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D240">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -3811,10 +3814,10 @@
         <v>2021</v>
       </c>
       <c r="B241" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C241" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D241">
         <v>0</v>
@@ -3825,10 +3828,10 @@
         <v>2021</v>
       </c>
       <c r="B242" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C242" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D242">
         <v>0</v>
@@ -3839,10 +3842,10 @@
         <v>2021</v>
       </c>
       <c r="B243" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C243" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D243">
         <v>0</v>
@@ -3853,13 +3856,13 @@
         <v>2021</v>
       </c>
       <c r="B244" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C244" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D244">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -3867,10 +3870,10 @@
         <v>2021</v>
       </c>
       <c r="B245" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C245" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D245">
         <v>0</v>
@@ -3881,10 +3884,10 @@
         <v>2021</v>
       </c>
       <c r="B246" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C246" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D246">
         <v>0</v>
@@ -3895,13 +3898,13 @@
         <v>2021</v>
       </c>
       <c r="B247" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C247" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D247">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -3909,10 +3912,10 @@
         <v>2021</v>
       </c>
       <c r="B248" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C248" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D248">
         <v>0</v>
@@ -3923,10 +3926,10 @@
         <v>2021</v>
       </c>
       <c r="B249" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C249" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D249">
         <v>0</v>
@@ -3937,10 +3940,10 @@
         <v>2021</v>
       </c>
       <c r="B250" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C250" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D250">
         <v>0</v>
@@ -3951,10 +3954,10 @@
         <v>2021</v>
       </c>
       <c r="B251" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C251" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D251">
         <v>0</v>
@@ -3965,10 +3968,10 @@
         <v>2021</v>
       </c>
       <c r="B252" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C252" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D252">
         <v>0</v>
@@ -3979,13 +3982,13 @@
         <v>2021</v>
       </c>
       <c r="B253" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C253" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D253">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -3993,13 +3996,13 @@
         <v>2021</v>
       </c>
       <c r="B254" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C254" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D254">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -4007,10 +4010,10 @@
         <v>2021</v>
       </c>
       <c r="B255" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C255" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D255">
         <v>0</v>
@@ -4021,10 +4024,10 @@
         <v>2021</v>
       </c>
       <c r="B256" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C256" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D256">
         <v>0</v>
@@ -4035,10 +4038,10 @@
         <v>2021</v>
       </c>
       <c r="B257" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C257" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D257">
         <v>0</v>
@@ -4049,13 +4052,13 @@
         <v>2021</v>
       </c>
       <c r="B258" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C258" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D258">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -4063,13 +4066,13 @@
         <v>2021</v>
       </c>
       <c r="B259" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C259" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D259">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -4077,10 +4080,10 @@
         <v>2021</v>
       </c>
       <c r="B260" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C260" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D260">
         <v>0</v>
@@ -4091,10 +4094,10 @@
         <v>2021</v>
       </c>
       <c r="B261" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C261" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D261">
         <v>0</v>
@@ -4105,10 +4108,10 @@
         <v>2021</v>
       </c>
       <c r="B262" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C262" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D262">
         <v>0</v>
@@ -4119,10 +4122,10 @@
         <v>2021</v>
       </c>
       <c r="B263" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C263" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D263">
         <v>0</v>
@@ -4133,10 +4136,10 @@
         <v>2021</v>
       </c>
       <c r="B264" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C264" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D264">
         <v>0</v>
@@ -4147,10 +4150,10 @@
         <v>2021</v>
       </c>
       <c r="B265" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C265" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D265">
         <v>0</v>
@@ -4161,13 +4164,13 @@
         <v>2021</v>
       </c>
       <c r="B266" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C266" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D266">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -4175,13 +4178,13 @@
         <v>2021</v>
       </c>
       <c r="B267" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C267" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D267">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -4189,13 +4192,13 @@
         <v>2021</v>
       </c>
       <c r="B268" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C268" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D268">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -4203,10 +4206,10 @@
         <v>2021</v>
       </c>
       <c r="B269" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C269" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D269">
         <v>0</v>
@@ -4217,10 +4220,10 @@
         <v>2021</v>
       </c>
       <c r="B270" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C270" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D270">
         <v>0</v>
@@ -4231,10 +4234,10 @@
         <v>2021</v>
       </c>
       <c r="B271" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C271" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D271">
         <v>0</v>
@@ -4245,10 +4248,10 @@
         <v>2021</v>
       </c>
       <c r="B272" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C272" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D272">
         <v>0</v>
@@ -4259,13 +4262,13 @@
         <v>2021</v>
       </c>
       <c r="B273" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C273" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D273">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -4273,52 +4276,52 @@
         <v>2021</v>
       </c>
       <c r="B274" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C274" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D274">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="275" spans="1:4">
       <c r="A275">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B275" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C275" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D275">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="276" spans="1:4">
       <c r="A276">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B276" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C276" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D276">
-        <v>150</v>
+        <v>0</v>
       </c>
     </row>
     <row r="277" spans="1:4">
       <c r="A277">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B277" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C277" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D277">
         <v>0</v>
@@ -4326,55 +4329,55 @@
     </row>
     <row r="278" spans="1:4">
       <c r="A278">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B278" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C278" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D278">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="279" spans="1:4">
       <c r="A279">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B279" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C279" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D279">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="280" spans="1:4">
       <c r="A280">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B280" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C280" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D280">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="281" spans="1:4">
       <c r="A281">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B281" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C281" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D281">
         <v>0</v>
@@ -4382,38 +4385,38 @@
     </row>
     <row r="282" spans="1:4">
       <c r="A282">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B282" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C282" t="s">
         <v>17</v>
       </c>
       <c r="D282">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="283" spans="1:4">
       <c r="A283">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B283" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C283" t="s">
         <v>18</v>
       </c>
       <c r="D283">
-        <v>100</v>
+        <v>5</v>
       </c>
     </row>
     <row r="284" spans="1:4">
       <c r="A284">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B284" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C284" t="s">
         <v>19</v>
@@ -4424,139 +4427,139 @@
     </row>
     <row r="285" spans="1:4">
       <c r="A285">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B285" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C285" t="s">
         <v>20</v>
       </c>
       <c r="D285">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="286" spans="1:4">
       <c r="A286">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B286" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C286" t="s">
         <v>21</v>
       </c>
       <c r="D286">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="287" spans="1:4">
       <c r="A287">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B287" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C287" t="s">
         <v>22</v>
       </c>
       <c r="D287">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="288" spans="1:4">
       <c r="A288">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B288" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C288" t="s">
         <v>23</v>
       </c>
       <c r="D288">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289" spans="1:4">
       <c r="A289">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B289" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C289" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D289">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="290" spans="1:4">
       <c r="A290">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B290" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C290" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D290">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="291" spans="1:4">
       <c r="A291">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B291" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C291" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D291">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="292" spans="1:4">
       <c r="A292">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B292" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C292" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D292">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="293" spans="1:4">
       <c r="A293">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B293" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C293" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D293">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="294" spans="1:4">
       <c r="A294">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B294" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C294" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D294">
         <v>0</v>
@@ -4564,13 +4567,13 @@
     </row>
     <row r="295" spans="1:4">
       <c r="A295">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B295" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C295" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D295">
         <v>0</v>
@@ -4578,41 +4581,41 @@
     </row>
     <row r="296" spans="1:4">
       <c r="A296">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B296" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C296" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D296">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297" spans="1:4">
       <c r="A297">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B297" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C297" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D297">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="298" spans="1:4">
       <c r="A298">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B298" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C298" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D298">
         <v>0</v>
@@ -4620,27 +4623,27 @@
     </row>
     <row r="299" spans="1:4">
       <c r="A299">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B299" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C299" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D299">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300" spans="1:4">
       <c r="A300">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B300" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C300" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D300">
         <v>0</v>
@@ -4648,13 +4651,13 @@
     </row>
     <row r="301" spans="1:4">
       <c r="A301">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B301" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C301" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D301">
         <v>0</v>
@@ -4662,27 +4665,27 @@
     </row>
     <row r="302" spans="1:4">
       <c r="A302">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B302" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C302" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D302">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="303" spans="1:4">
       <c r="A303">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B303" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C303" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D303">
         <v>0</v>
@@ -4690,13 +4693,13 @@
     </row>
     <row r="304" spans="1:4">
       <c r="A304">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B304" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C304" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D304">
         <v>0</v>
@@ -4704,13 +4707,13 @@
     </row>
     <row r="305" spans="1:4">
       <c r="A305">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B305" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C305" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D305">
         <v>0</v>
@@ -4718,13 +4721,13 @@
     </row>
     <row r="306" spans="1:4">
       <c r="A306">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B306" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C306" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D306">
         <v>0</v>
@@ -4732,13 +4735,13 @@
     </row>
     <row r="307" spans="1:4">
       <c r="A307">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B307" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C307" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D307">
         <v>0</v>
@@ -4746,13 +4749,13 @@
     </row>
     <row r="308" spans="1:4">
       <c r="A308">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B308" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C308" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D308">
         <v>0</v>
@@ -4760,13 +4763,13 @@
     </row>
     <row r="309" spans="1:4">
       <c r="A309">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B309" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C309" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D309">
         <v>0</v>
@@ -4774,13 +4777,13 @@
     </row>
     <row r="310" spans="1:4">
       <c r="A310">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B310" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C310" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D310">
         <v>0</v>
@@ -4788,13 +4791,13 @@
     </row>
     <row r="311" spans="1:4">
       <c r="A311">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B311" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C311" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D311">
         <v>0</v>
@@ -4802,30 +4805,30 @@
     </row>
     <row r="312" spans="1:4">
       <c r="A312">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B312" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C312" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D312">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="313" spans="1:4">
       <c r="A313">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B313" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C313" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D313">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -4833,13 +4836,13 @@
         <v>2022</v>
       </c>
       <c r="B314" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C314" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D314">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -4847,13 +4850,13 @@
         <v>2022</v>
       </c>
       <c r="B315" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C315" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D315">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -4861,13 +4864,13 @@
         <v>2022</v>
       </c>
       <c r="B316" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C316" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D316">
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -4875,10 +4878,10 @@
         <v>2022</v>
       </c>
       <c r="B317" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C317" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D317">
         <v>0</v>
@@ -4889,13 +4892,13 @@
         <v>2022</v>
       </c>
       <c r="B318" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C318" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D318">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -4903,13 +4906,13 @@
         <v>2022</v>
       </c>
       <c r="B319" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C319" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D319">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -4917,13 +4920,13 @@
         <v>2022</v>
       </c>
       <c r="B320" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C320" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D320">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -4931,10 +4934,10 @@
         <v>2022</v>
       </c>
       <c r="B321" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C321" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D321">
         <v>0</v>
@@ -4945,13 +4948,13 @@
         <v>2022</v>
       </c>
       <c r="B322" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C322" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D322">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -4959,13 +4962,13 @@
         <v>2022</v>
       </c>
       <c r="B323" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C323" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D323">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -4973,13 +4976,13 @@
         <v>2022</v>
       </c>
       <c r="B324" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C324" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D324">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -4987,13 +4990,13 @@
         <v>2022</v>
       </c>
       <c r="B325" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C325" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D325">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -5001,13 +5004,13 @@
         <v>2022</v>
       </c>
       <c r="B326" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C326" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D326">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -5015,13 +5018,13 @@
         <v>2022</v>
       </c>
       <c r="B327" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C327" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D327">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -5029,13 +5032,13 @@
         <v>2022</v>
       </c>
       <c r="B328" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C328" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D328">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -5043,13 +5046,13 @@
         <v>2022</v>
       </c>
       <c r="B329" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C329" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D329">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -5057,13 +5060,13 @@
         <v>2022</v>
       </c>
       <c r="B330" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C330" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D330">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -5071,13 +5074,13 @@
         <v>2022</v>
       </c>
       <c r="B331" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C331" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D331">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -5085,13 +5088,13 @@
         <v>2022</v>
       </c>
       <c r="B332" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C332" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D332">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -5099,10 +5102,10 @@
         <v>2022</v>
       </c>
       <c r="B333" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C333" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D333">
         <v>0</v>
@@ -5113,13 +5116,13 @@
         <v>2022</v>
       </c>
       <c r="B334" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C334" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D334">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -5127,13 +5130,13 @@
         <v>2022</v>
       </c>
       <c r="B335" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C335" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D335">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -5141,10 +5144,10 @@
         <v>2022</v>
       </c>
       <c r="B336" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C336" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D336">
         <v>0</v>
@@ -5155,10 +5158,10 @@
         <v>2022</v>
       </c>
       <c r="B337" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C337" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D337">
         <v>0</v>
@@ -5169,7 +5172,7 @@
         <v>2022</v>
       </c>
       <c r="B338" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C338" t="s">
         <v>17</v>
@@ -5183,13 +5186,13 @@
         <v>2022</v>
       </c>
       <c r="B339" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C339" t="s">
         <v>18</v>
       </c>
       <c r="D339">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -5197,13 +5200,13 @@
         <v>2022</v>
       </c>
       <c r="B340" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C340" t="s">
         <v>19</v>
       </c>
       <c r="D340">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -5211,13 +5214,13 @@
         <v>2022</v>
       </c>
       <c r="B341" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C341" t="s">
         <v>20</v>
       </c>
       <c r="D341">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -5225,13 +5228,13 @@
         <v>2022</v>
       </c>
       <c r="B342" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C342" t="s">
         <v>21</v>
       </c>
       <c r="D342">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -5239,13 +5242,13 @@
         <v>2022</v>
       </c>
       <c r="B343" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C343" t="s">
         <v>22</v>
       </c>
       <c r="D343">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -5253,7 +5256,7 @@
         <v>2022</v>
       </c>
       <c r="B344" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C344" t="s">
         <v>23</v>
@@ -5267,13 +5270,13 @@
         <v>2022</v>
       </c>
       <c r="B345" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C345" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D345">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -5281,10 +5284,10 @@
         <v>2022</v>
       </c>
       <c r="B346" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C346" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D346">
         <v>0</v>
@@ -5295,10 +5298,10 @@
         <v>2022</v>
       </c>
       <c r="B347" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C347" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D347">
         <v>0</v>
@@ -5309,10 +5312,10 @@
         <v>2022</v>
       </c>
       <c r="B348" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C348" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D348">
         <v>0</v>
@@ -5323,10 +5326,10 @@
         <v>2022</v>
       </c>
       <c r="B349" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C349" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D349">
         <v>0</v>
@@ -5337,10 +5340,10 @@
         <v>2022</v>
       </c>
       <c r="B350" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C350" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D350">
         <v>0</v>
@@ -5351,10 +5354,10 @@
         <v>2022</v>
       </c>
       <c r="B351" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C351" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D351">
         <v>0</v>
@@ -5365,10 +5368,10 @@
         <v>2022</v>
       </c>
       <c r="B352" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C352" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D352">
         <v>0</v>
@@ -5379,10 +5382,10 @@
         <v>2022</v>
       </c>
       <c r="B353" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C353" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D353">
         <v>0</v>
@@ -5393,10 +5396,10 @@
         <v>2022</v>
       </c>
       <c r="B354" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C354" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D354">
         <v>0</v>
@@ -5407,10 +5410,10 @@
         <v>2022</v>
       </c>
       <c r="B355" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C355" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D355">
         <v>0</v>
@@ -5421,10 +5424,10 @@
         <v>2022</v>
       </c>
       <c r="B356" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C356" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D356">
         <v>0</v>
@@ -5435,10 +5438,10 @@
         <v>2022</v>
       </c>
       <c r="B357" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C357" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D357">
         <v>0</v>
@@ -5449,10 +5452,10 @@
         <v>2022</v>
       </c>
       <c r="B358" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C358" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D358">
         <v>0</v>
@@ -5463,10 +5466,10 @@
         <v>2022</v>
       </c>
       <c r="B359" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C359" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D359">
         <v>0</v>
@@ -5477,10 +5480,10 @@
         <v>2022</v>
       </c>
       <c r="B360" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C360" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D360">
         <v>0</v>
@@ -5491,10 +5494,10 @@
         <v>2022</v>
       </c>
       <c r="B361" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C361" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D361">
         <v>0</v>
@@ -5505,13 +5508,13 @@
         <v>2022</v>
       </c>
       <c r="B362" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C362" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D362">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -5519,10 +5522,10 @@
         <v>2022</v>
       </c>
       <c r="B363" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C363" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D363">
         <v>0</v>
@@ -5533,10 +5536,10 @@
         <v>2022</v>
       </c>
       <c r="B364" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C364" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D364">
         <v>0</v>
@@ -5547,12 +5550,740 @@
         <v>2022</v>
       </c>
       <c r="B365" t="s">
+        <v>10</v>
+      </c>
+      <c r="C365" t="s">
+        <v>20</v>
+      </c>
+      <c r="D365">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4">
+      <c r="A366">
+        <v>2022</v>
+      </c>
+      <c r="B366" t="s">
+        <v>10</v>
+      </c>
+      <c r="C366" t="s">
+        <v>21</v>
+      </c>
+      <c r="D366">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4">
+      <c r="A367">
+        <v>2022</v>
+      </c>
+      <c r="B367" t="s">
+        <v>10</v>
+      </c>
+      <c r="C367" t="s">
+        <v>22</v>
+      </c>
+      <c r="D367">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4">
+      <c r="A368">
+        <v>2022</v>
+      </c>
+      <c r="B368" t="s">
+        <v>10</v>
+      </c>
+      <c r="C368" t="s">
+        <v>23</v>
+      </c>
+      <c r="D368">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4">
+      <c r="A369">
+        <v>2022</v>
+      </c>
+      <c r="B369" t="s">
+        <v>10</v>
+      </c>
+      <c r="C369" t="s">
+        <v>24</v>
+      </c>
+      <c r="D369">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4">
+      <c r="A370">
+        <v>2022</v>
+      </c>
+      <c r="B370" t="s">
+        <v>11</v>
+      </c>
+      <c r="C370" t="s">
+        <v>17</v>
+      </c>
+      <c r="D370">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4">
+      <c r="A371">
+        <v>2022</v>
+      </c>
+      <c r="B371" t="s">
+        <v>11</v>
+      </c>
+      <c r="C371" t="s">
+        <v>18</v>
+      </c>
+      <c r="D371">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4">
+      <c r="A372">
+        <v>2022</v>
+      </c>
+      <c r="B372" t="s">
+        <v>11</v>
+      </c>
+      <c r="C372" t="s">
+        <v>19</v>
+      </c>
+      <c r="D372">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4">
+      <c r="A373">
+        <v>2022</v>
+      </c>
+      <c r="B373" t="s">
+        <v>11</v>
+      </c>
+      <c r="C373" t="s">
+        <v>20</v>
+      </c>
+      <c r="D373">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4">
+      <c r="A374">
+        <v>2022</v>
+      </c>
+      <c r="B374" t="s">
+        <v>11</v>
+      </c>
+      <c r="C374" t="s">
+        <v>21</v>
+      </c>
+      <c r="D374">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4">
+      <c r="A375">
+        <v>2022</v>
+      </c>
+      <c r="B375" t="s">
+        <v>11</v>
+      </c>
+      <c r="C375" t="s">
+        <v>22</v>
+      </c>
+      <c r="D375">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4">
+      <c r="A376">
+        <v>2022</v>
+      </c>
+      <c r="B376" t="s">
+        <v>11</v>
+      </c>
+      <c r="C376" t="s">
+        <v>23</v>
+      </c>
+      <c r="D376">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4">
+      <c r="A377">
+        <v>2022</v>
+      </c>
+      <c r="B377" t="s">
+        <v>11</v>
+      </c>
+      <c r="C377" t="s">
+        <v>24</v>
+      </c>
+      <c r="D377">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4">
+      <c r="A378">
+        <v>2022</v>
+      </c>
+      <c r="B378" t="s">
+        <v>12</v>
+      </c>
+      <c r="C378" t="s">
+        <v>17</v>
+      </c>
+      <c r="D378">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4">
+      <c r="A379">
+        <v>2022</v>
+      </c>
+      <c r="B379" t="s">
+        <v>12</v>
+      </c>
+      <c r="C379" t="s">
+        <v>18</v>
+      </c>
+      <c r="D379">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4">
+      <c r="A380">
+        <v>2022</v>
+      </c>
+      <c r="B380" t="s">
+        <v>12</v>
+      </c>
+      <c r="C380" t="s">
+        <v>19</v>
+      </c>
+      <c r="D380">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4">
+      <c r="A381">
+        <v>2022</v>
+      </c>
+      <c r="B381" t="s">
+        <v>12</v>
+      </c>
+      <c r="C381" t="s">
+        <v>20</v>
+      </c>
+      <c r="D381">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4">
+      <c r="A382">
+        <v>2022</v>
+      </c>
+      <c r="B382" t="s">
+        <v>12</v>
+      </c>
+      <c r="C382" t="s">
+        <v>21</v>
+      </c>
+      <c r="D382">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4">
+      <c r="A383">
+        <v>2022</v>
+      </c>
+      <c r="B383" t="s">
+        <v>12</v>
+      </c>
+      <c r="C383" t="s">
+        <v>22</v>
+      </c>
+      <c r="D383">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4">
+      <c r="A384">
+        <v>2022</v>
+      </c>
+      <c r="B384" t="s">
+        <v>12</v>
+      </c>
+      <c r="C384" t="s">
+        <v>23</v>
+      </c>
+      <c r="D384">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4">
+      <c r="A385">
+        <v>2022</v>
+      </c>
+      <c r="B385" t="s">
+        <v>12</v>
+      </c>
+      <c r="C385" t="s">
+        <v>24</v>
+      </c>
+      <c r="D385">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4">
+      <c r="A386">
+        <v>2022</v>
+      </c>
+      <c r="B386" t="s">
+        <v>13</v>
+      </c>
+      <c r="C386" t="s">
+        <v>17</v>
+      </c>
+      <c r="D386">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4">
+      <c r="A387">
+        <v>2022</v>
+      </c>
+      <c r="B387" t="s">
+        <v>13</v>
+      </c>
+      <c r="C387" t="s">
+        <v>18</v>
+      </c>
+      <c r="D387">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4">
+      <c r="A388">
+        <v>2022</v>
+      </c>
+      <c r="B388" t="s">
+        <v>13</v>
+      </c>
+      <c r="C388" t="s">
+        <v>19</v>
+      </c>
+      <c r="D388">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4">
+      <c r="A389">
+        <v>2022</v>
+      </c>
+      <c r="B389" t="s">
+        <v>13</v>
+      </c>
+      <c r="C389" t="s">
+        <v>20</v>
+      </c>
+      <c r="D389">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4">
+      <c r="A390">
+        <v>2022</v>
+      </c>
+      <c r="B390" t="s">
+        <v>13</v>
+      </c>
+      <c r="C390" t="s">
+        <v>21</v>
+      </c>
+      <c r="D390">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4">
+      <c r="A391">
+        <v>2022</v>
+      </c>
+      <c r="B391" t="s">
+        <v>13</v>
+      </c>
+      <c r="C391" t="s">
+        <v>22</v>
+      </c>
+      <c r="D391">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4">
+      <c r="A392">
+        <v>2022</v>
+      </c>
+      <c r="B392" t="s">
+        <v>13</v>
+      </c>
+      <c r="C392" t="s">
+        <v>23</v>
+      </c>
+      <c r="D392">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4">
+      <c r="A393">
+        <v>2022</v>
+      </c>
+      <c r="B393" t="s">
+        <v>13</v>
+      </c>
+      <c r="C393" t="s">
+        <v>24</v>
+      </c>
+      <c r="D393">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4">
+      <c r="A394">
+        <v>2022</v>
+      </c>
+      <c r="B394" t="s">
+        <v>14</v>
+      </c>
+      <c r="C394" t="s">
+        <v>17</v>
+      </c>
+      <c r="D394">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4">
+      <c r="A395">
+        <v>2022</v>
+      </c>
+      <c r="B395" t="s">
+        <v>14</v>
+      </c>
+      <c r="C395" t="s">
+        <v>18</v>
+      </c>
+      <c r="D395">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4">
+      <c r="A396">
+        <v>2022</v>
+      </c>
+      <c r="B396" t="s">
+        <v>14</v>
+      </c>
+      <c r="C396" t="s">
+        <v>19</v>
+      </c>
+      <c r="D396">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4">
+      <c r="A397">
+        <v>2022</v>
+      </c>
+      <c r="B397" t="s">
+        <v>14</v>
+      </c>
+      <c r="C397" t="s">
+        <v>20</v>
+      </c>
+      <c r="D397">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4">
+      <c r="A398">
+        <v>2022</v>
+      </c>
+      <c r="B398" t="s">
+        <v>14</v>
+      </c>
+      <c r="C398" t="s">
+        <v>21</v>
+      </c>
+      <c r="D398">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4">
+      <c r="A399">
+        <v>2022</v>
+      </c>
+      <c r="B399" t="s">
+        <v>14</v>
+      </c>
+      <c r="C399" t="s">
+        <v>22</v>
+      </c>
+      <c r="D399">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4">
+      <c r="A400">
+        <v>2022</v>
+      </c>
+      <c r="B400" t="s">
+        <v>14</v>
+      </c>
+      <c r="C400" t="s">
+        <v>23</v>
+      </c>
+      <c r="D400">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4">
+      <c r="A401">
+        <v>2022</v>
+      </c>
+      <c r="B401" t="s">
+        <v>14</v>
+      </c>
+      <c r="C401" t="s">
+        <v>24</v>
+      </c>
+      <c r="D401">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4">
+      <c r="A402">
+        <v>2022</v>
+      </c>
+      <c r="B402" t="s">
+        <v>15</v>
+      </c>
+      <c r="C402" t="s">
+        <v>17</v>
+      </c>
+      <c r="D402">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4">
+      <c r="A403">
+        <v>2022</v>
+      </c>
+      <c r="B403" t="s">
+        <v>15</v>
+      </c>
+      <c r="C403" t="s">
+        <v>18</v>
+      </c>
+      <c r="D403">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4">
+      <c r="A404">
+        <v>2022</v>
+      </c>
+      <c r="B404" t="s">
+        <v>15</v>
+      </c>
+      <c r="C404" t="s">
+        <v>19</v>
+      </c>
+      <c r="D404">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4">
+      <c r="A405">
+        <v>2022</v>
+      </c>
+      <c r="B405" t="s">
+        <v>15</v>
+      </c>
+      <c r="C405" t="s">
+        <v>20</v>
+      </c>
+      <c r="D405">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4">
+      <c r="A406">
+        <v>2022</v>
+      </c>
+      <c r="B406" t="s">
+        <v>15</v>
+      </c>
+      <c r="C406" t="s">
+        <v>21</v>
+      </c>
+      <c r="D406">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4">
+      <c r="A407">
+        <v>2022</v>
+      </c>
+      <c r="B407" t="s">
+        <v>15</v>
+      </c>
+      <c r="C407" t="s">
+        <v>22</v>
+      </c>
+      <c r="D407">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4">
+      <c r="A408">
+        <v>2022</v>
+      </c>
+      <c r="B408" t="s">
+        <v>15</v>
+      </c>
+      <c r="C408" t="s">
+        <v>23</v>
+      </c>
+      <c r="D408">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4">
+      <c r="A409">
+        <v>2022</v>
+      </c>
+      <c r="B409" t="s">
+        <v>15</v>
+      </c>
+      <c r="C409" t="s">
+        <v>24</v>
+      </c>
+      <c r="D409">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4">
+      <c r="A410">
+        <v>2022</v>
+      </c>
+      <c r="B410" t="s">
         <v>16</v>
       </c>
-      <c r="C365" t="s">
+      <c r="C410" t="s">
+        <v>17</v>
+      </c>
+      <c r="D410">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4">
+      <c r="A411">
+        <v>2022</v>
+      </c>
+      <c r="B411" t="s">
+        <v>16</v>
+      </c>
+      <c r="C411" t="s">
+        <v>18</v>
+      </c>
+      <c r="D411">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4">
+      <c r="A412">
+        <v>2022</v>
+      </c>
+      <c r="B412" t="s">
+        <v>16</v>
+      </c>
+      <c r="C412" t="s">
+        <v>19</v>
+      </c>
+      <c r="D412">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4">
+      <c r="A413">
+        <v>2022</v>
+      </c>
+      <c r="B413" t="s">
+        <v>16</v>
+      </c>
+      <c r="C413" t="s">
+        <v>20</v>
+      </c>
+      <c r="D413">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4">
+      <c r="A414">
+        <v>2022</v>
+      </c>
+      <c r="B414" t="s">
+        <v>16</v>
+      </c>
+      <c r="C414" t="s">
+        <v>21</v>
+      </c>
+      <c r="D414">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4">
+      <c r="A415">
+        <v>2022</v>
+      </c>
+      <c r="B415" t="s">
+        <v>16</v>
+      </c>
+      <c r="C415" t="s">
+        <v>22</v>
+      </c>
+      <c r="D415">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4">
+      <c r="A416">
+        <v>2022</v>
+      </c>
+      <c r="B416" t="s">
+        <v>16</v>
+      </c>
+      <c r="C416" t="s">
         <v>23</v>
       </c>
-      <c r="D365">
+      <c r="D416">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4">
+      <c r="A417">
+        <v>2022</v>
+      </c>
+      <c r="B417" t="s">
+        <v>16</v>
+      </c>
+      <c r="C417" t="s">
+        <v>24</v>
+      </c>
+      <c r="D417">
         <v>300</v>
       </c>
     </row>
